--- a/data/trans_dic/P25A$molestias-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25A$molestias-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,33; 23,07</t>
+          <t>14,17; 23,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,67; 15,71</t>
+          <t>9,06; 16,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,29; 24,61</t>
+          <t>14,58; 24,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 22,88</t>
+          <t>4,11; 22,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,83</t>
+          <t>0,0; 10,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,92; 38,18</t>
+          <t>10,26; 37,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,83; 21,8</t>
+          <t>13,9; 22,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,86; 13,99</t>
+          <t>7,8; 13,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,08; 24,86</t>
+          <t>15,25; 25,36</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,84; 26,97</t>
+          <t>16,01; 26,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 14,26</t>
+          <t>7,28; 14,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,78; 20,11</t>
+          <t>11,76; 20,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,02; 20,96</t>
+          <t>10,27; 22,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 13,12</t>
+          <t>5,27; 13,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,26; 19,58</t>
+          <t>9,53; 19,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,97; 23,03</t>
+          <t>14,82; 22,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 12,3</t>
+          <t>6,99; 12,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,33; 18,25</t>
+          <t>11,92; 18,02</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,31; 23,14</t>
+          <t>7,12; 23,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 12,64</t>
+          <t>2,39; 13,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 17,47</t>
+          <t>2,64; 16,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 27,7</t>
+          <t>7,75; 28,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,57; 26,32</t>
+          <t>7,94; 25,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 17,58</t>
+          <t>5,3; 17,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,61; 21,62</t>
+          <t>9,5; 21,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 15,97</t>
+          <t>6,15; 16,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 14,5</t>
+          <t>5,82; 15,39</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,74; 21,93</t>
+          <t>15,98; 22,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,52; 13,2</t>
+          <t>8,56; 12,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,68; 18,74</t>
+          <t>12,99; 19,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,4; 19,27</t>
+          <t>10,33; 18,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,35; 12,83</t>
+          <t>6,18; 12,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,04; 17,77</t>
+          <t>10,19; 18,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,25; 20,38</t>
+          <t>15,15; 20,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,33; 11,93</t>
+          <t>8,35; 12,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,63; 17,4</t>
+          <t>12,66; 17,46</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43419; 69929</t>
+          <t>42932; 69770</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32255; 58466</t>
+          <t>33701; 60284</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29979; 51643</t>
+          <t>30595; 52262</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1941; 11017</t>
+          <t>1978; 10981</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6787</t>
+          <t>0; 6950</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3733; 14368</t>
+          <t>3863; 14033</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48573; 76553</t>
+          <t>48818; 78016</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34659; 61718</t>
+          <t>34427; 61203</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37324; 61522</t>
+          <t>37731; 62753</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37562; 63942</t>
+          <t>37959; 62318</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26063; 49604</t>
+          <t>25312; 49763</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35594; 60748</t>
+          <t>35531; 61192</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15145; 31693</t>
+          <t>15523; 33759</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12530; 31489</t>
+          <t>12660; 31292</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18617; 39369</t>
+          <t>19157; 39030</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58112; 89406</t>
+          <t>57541; 88567</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41383; 72309</t>
+          <t>41099; 72172</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56984; 91840</t>
+          <t>59979; 90670</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6168; 19538</t>
+          <t>6015; 19643</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2751; 12166</t>
+          <t>2302; 12775</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3190; 15658</t>
+          <t>2366; 14782</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4071; 14228</t>
+          <t>3981; 14512</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6633; 20375</t>
+          <t>6147; 19486</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4984; 16716</t>
+          <t>5041; 16951</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11692; 29361</t>
+          <t>12906; 28947</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11081; 27728</t>
+          <t>10683; 28325</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9911; 26777</t>
+          <t>10743; 28419</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>98278; 136992</t>
+          <t>99837; 137503</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69519; 107720</t>
+          <t>69852; 104258</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76294; 112714</t>
+          <t>78131; 114668</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26066; 48311</t>
+          <t>25904; 47492</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24537; 49587</t>
+          <t>23883; 48479</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33513; 59302</t>
+          <t>34005; 60149</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>133501; 178395</t>
+          <t>132571; 176070</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100155; 143504</t>
+          <t>100440; 145462</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>118159; 162689</t>
+          <t>118433; 163259</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$molestias-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25A$molestias-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,17; 23,02</t>
+          <t>14,57; 23,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,06; 16,2</t>
+          <t>8,71; 15,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,58; 24,91</t>
+          <t>14,5; 24,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 22,8</t>
+          <t>5,68; 22,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,06</t>
+          <t>0,0; 8,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,26; 37,29</t>
+          <t>10,31; 35,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,9; 22,21</t>
+          <t>14,13; 21,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,8; 13,87</t>
+          <t>7,91; 13,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,25; 25,36</t>
+          <t>15,58; 24,98</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,01; 26,29</t>
+          <t>16,17; 26,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,28; 14,31</t>
+          <t>7,22; 13,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,76; 20,26</t>
+          <t>11,61; 20,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,27; 22,33</t>
+          <t>9,52; 21,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 13,03</t>
+          <t>5,02; 13,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,53; 19,41</t>
+          <t>9,16; 18,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,82; 22,81</t>
+          <t>15,07; 23,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,99; 12,28</t>
+          <t>7,03; 12,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,92; 18,02</t>
+          <t>11,89; 18,32</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 23,26</t>
+          <t>6,93; 23,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 13,27</t>
+          <t>2,37; 13,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 16,5</t>
+          <t>3,18; 17,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 28,25</t>
+          <t>7,35; 27,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,94; 25,17</t>
+          <t>8,02; 25,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 17,83</t>
+          <t>5,29; 18,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,5; 21,32</t>
+          <t>9,58; 21,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,15; 16,31</t>
+          <t>6,57; 15,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 15,39</t>
+          <t>5,48; 14,8</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,98; 22,02</t>
+          <t>15,9; 22,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,56; 12,78</t>
+          <t>8,59; 12,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,99; 19,06</t>
+          <t>13,05; 19,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,33; 18,94</t>
+          <t>10,68; 19,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,18; 12,54</t>
+          <t>5,96; 12,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,19; 18,02</t>
+          <t>10,53; 17,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,15; 20,12</t>
+          <t>15,24; 20,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,35; 12,1</t>
+          <t>8,31; 11,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,66; 17,46</t>
+          <t>12,63; 17,37</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>42932; 69770</t>
+          <t>44161; 70061</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33701; 60284</t>
+          <t>32422; 58041</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30595; 52262</t>
+          <t>30416; 51634</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1978; 10981</t>
+          <t>2736; 11006</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6950</t>
+          <t>0; 6075</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3863; 14033</t>
+          <t>3880; 13462</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48818; 78016</t>
+          <t>49636; 76311</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34427; 61203</t>
+          <t>34900; 60974</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37731; 62753</t>
+          <t>38559; 61805</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37959; 62318</t>
+          <t>38328; 62703</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25312; 49763</t>
+          <t>25122; 48462</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35531; 61192</t>
+          <t>35064; 62733</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15523; 33759</t>
+          <t>14389; 32915</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12660; 31292</t>
+          <t>12043; 32185</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19157; 39030</t>
+          <t>18411; 37975</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57541; 88567</t>
+          <t>58513; 90232</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41099; 72172</t>
+          <t>41307; 72378</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59979; 90670</t>
+          <t>59816; 92147</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6015; 19643</t>
+          <t>5852; 19650</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2302; 12775</t>
+          <t>2283; 12896</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2366; 14782</t>
+          <t>2848; 15346</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3981; 14512</t>
+          <t>3776; 14244</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6147; 19486</t>
+          <t>6207; 19978</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5041; 16951</t>
+          <t>5027; 17810</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12906; 28947</t>
+          <t>13008; 29129</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10683; 28325</t>
+          <t>11401; 27113</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10743; 28419</t>
+          <t>10122; 27339</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>99837; 137503</t>
+          <t>99299; 139156</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69852; 104258</t>
+          <t>70060; 105400</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78131; 114668</t>
+          <t>78509; 114296</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25904; 47492</t>
+          <t>26767; 48486</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23883; 48479</t>
+          <t>23031; 48870</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34005; 60149</t>
+          <t>35152; 59471</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>132571; 176070</t>
+          <t>133355; 177937</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100440; 145462</t>
+          <t>99887; 144016</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>118433; 163259</t>
+          <t>118097; 162470</t>
         </is>
       </c>
     </row>
